--- a/annotation_tool/annotation_template.xlsx
+++ b/annotation_tool/annotation_template.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/heste/workspace/sn-caption/annotation_tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831C4AD8-2325-EA40-BFE6-1BAE507E0F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC121F6F-2392-7541-93C6-496A58E39BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5780" yWindow="-28300" windowWidth="33600" windowHeight="13980" activeTab="1" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
+    <workbookView xWindow="-14660" yWindow="-28180" windowWidth="33940" windowHeight="14020" activeTab="1" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート" sheetId="4" r:id="rId1"/>
-    <sheet name="moriy" sheetId="5" r:id="rId2"/>
+    <sheet name="テンプレート_seed10" sheetId="6" r:id="rId2"/>
+    <sheet name="moriy" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="1">moriy!$A$1:$H$101</definedName>
+    <definedName name="_10_denoised_1_tokenized_224p_annotation" localSheetId="1">テンプレート_seed10!$A$1:$H$101</definedName>
+    <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="2">moriy!$A$1:$H$101</definedName>
     <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="0">テンプレート!$A$1:$H$101</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +45,21 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{2947C2F0-C812-C44E-8E0B-F2D00BC96894}" name="denoised_1_tokenized_224p_annotation1" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="1" xr16:uid="{DED3BFDE-FE8B-444E-9992-18E390A2A210}" name="10_denoised_1_tokenized_224p_annotation" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="65001" sourceFile="/Users/heste/workspace/sn-caption/data/10_denoised_1_tokenized_224p_annotation.csv" tab="0" comma="1">
+      <textFields count="8">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="2" xr16:uid="{2947C2F0-C812-C44E-8E0B-F2D00BC96894}" name="denoised_1_tokenized_224p_annotation1" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="/Users/heste/workspace/sn-caption/data/denoised_1_tokenized_224p_annotation.csv" tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -56,7 +73,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" xr16:uid="{6CA83349-B20A-414D-BA20-B259599B563B}" name="denoised_1_tokenized_224p_annotation11" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="3" xr16:uid="{6CA83349-B20A-414D-BA20-B259599B563B}" name="denoised_1_tokenized_224p_annotation11" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="/Users/heste/workspace/sn-caption/data/denoised_1_tokenized_224p_annotation.csv" tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -74,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="428">
   <si>
     <t>id</t>
   </si>
@@ -1043,6 +1060,382 @@
       <t xml:space="preserve">カンソウ </t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実況者はwouldのつもりでwillって言ってそう（口語表現？）</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ジッキョウｓｈ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">シャ </t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t xml:space="preserve">イッテソウ </t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t xml:space="preserve">コウゴヒョウゲン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>he 困る</t>
+    <rPh sb="3" eb="4">
+      <t xml:space="preserve">コマル </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>And the Argentine is enjoying quite a renaissance at the moment.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>迷った。2ぽいかも</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">マヨッタ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gignac arrives and Gignac scores!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>spy =&gt; spike?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Petrushan has to score again.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>付加的情報混じりの感想</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">フカテキジョウホウ </t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t xml:space="preserve">マジリノカンソウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>迷</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1と迷った</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>罵倒の意を込めた比喩表現</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">バトウ </t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t xml:space="preserve">ヒユヒョウゲン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ちょいノイズ？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Now a idea.</t>
+  </si>
+  <si>
+    <t>He's smart because he's a fake.</t>
+  </si>
+  <si>
+    <t>It's Alaba and Alonso at the heart of that by in defence so it is very much unfamiliar looking defensive line for the home side.</t>
+  </si>
+  <si>
+    <t>When we say holding in the box, we're not talking about a foul now.</t>
+  </si>
+  <si>
+    <t>2015-02-15 - 14-30 AC Milan 1 - 1 Empoli</t>
+  </si>
+  <si>
+    <t>...Menes really is the... ...inspiration for Milan... ...at the moment.</t>
+  </si>
+  <si>
+    <t>Dani Alves is trying to score.</t>
+  </si>
+  <si>
+    <t>Alexander has a problem with the ball.</t>
+  </si>
+  <si>
+    <t>He became much coveted after his time at Southampton, which began here.</t>
+  </si>
+  <si>
+    <t>Mkhmedi.</t>
+  </si>
+  <si>
+    <t>The number 19 Ivan Cavallero.</t>
+  </si>
+  <si>
+    <t>Ronaldo got a hat-trick that day as I mentioned.</t>
+  </si>
+  <si>
+    <t>Marcelo wanted to leave first for Kroos, he gives it directly to the rival.</t>
+  </si>
+  <si>
+    <t>Now the counter-attack.</t>
+  </si>
+  <si>
+    <t>He's been controlling all these things.</t>
+  </si>
+  <si>
+    <t>Kjezo again.</t>
+  </si>
+  <si>
+    <t>Paderborn from the beginning with a clear defense concept.</t>
+  </si>
+  <si>
+    <t>Koke.</t>
+  </si>
+  <si>
+    <t>He shot from a distance.</t>
+  </si>
+  <si>
+    <t>The problem for FC Barcelona is Alventosa's presence.</t>
+  </si>
+  <si>
+    <t>Calcio is returning, which, I think, all fans of the series are very happy about.</t>
+  </si>
+  <si>
+    <t>Hey!</t>
+  </si>
+  <si>
+    <t>Hasn't yet been a break in play.</t>
+  </si>
+  <si>
+    <t>Dani Alves is playing with a traditional Juventus' style.</t>
+  </si>
+  <si>
+    <t>I don't think so.</t>
+  </si>
+  <si>
+    <t>The Zinedine Zidane team are trying to get the ball out, Toni Kroos is looking for it, it's a bad pass.</t>
+  </si>
+  <si>
+    <t>Now Hulk up.</t>
+  </si>
+  <si>
+    <t>And then the non-rule climbing handball.</t>
+  </si>
+  <si>
+    <t>Vidal.</t>
+  </si>
+  <si>
+    <t>Does the little pass inside.</t>
+  </si>
+  <si>
+    <t>Depor will come out obviously looking to defend their goal especially over the first 20 minutes or so.</t>
+  </si>
+  <si>
+    <t>There was no flag.</t>
+  </si>
+  <si>
+    <t>Chelsea in those wide areas.</t>
+  </si>
+  <si>
+    <t>Everything you can win by 1-0 is always very dangerous.</t>
+  </si>
+  <si>
+    <t>The player of the German national team scores the first Juventus ball in the new season.</t>
+  </si>
+  <si>
+    <t>So good start here for the Galicians.</t>
+  </si>
+  <si>
+    <t>Rakitic.</t>
+  </si>
+  <si>
+    <t>Another long ball.</t>
+  </si>
+  <si>
+    <t>Mario Götze is left to Stefan Ilsenker.</t>
+  </si>
+  <si>
+    <t>Nacho outside to the Brazilian left back.</t>
+  </si>
+  <si>
+    <t>Good wall from Bernardeschi.</t>
+  </si>
+  <si>
+    <t>Shaquille has failed.</t>
+  </si>
+  <si>
+    <t>Burak is turning.</t>
+  </si>
+  <si>
+    <t>He scored a yellow-red goal in Lviv.</t>
+  </si>
+  <si>
+    <t>Ribéry, quickly with Lewandowski.</t>
+  </si>
+  <si>
+    <t>He shoots the header.</t>
+  </si>
+  <si>
+    <t>I think he's capable of it.</t>
+  </si>
+  <si>
+    <t>That's why the great good of European football covered his signature.</t>
+  </si>
+  <si>
+    <t>Trapp!</t>
+  </si>
+  <si>
+    <t>But I think everybody knew Cristiano Ronaldo was going to go for goal from that position.</t>
+  </si>
+  <si>
+    <t>It's going to move.</t>
+  </si>
+  <si>
+    <t>And got themselves right back in the game.</t>
+  </si>
+  <si>
+    <t>Although it's just going to beat Marquinhos.</t>
+  </si>
+  <si>
+    <t>Chalhanoglu helps it on towards Kiesling.</t>
+  </si>
+  <si>
+    <t>I must say that they are taking advantage of the change of rules.</t>
+  </si>
+  <si>
+    <t>This is not good for PSG.</t>
+  </si>
+  <si>
+    <t>The ball continues to be on the left side.</t>
+  </si>
+  <si>
+    <t>Hilbert under pressure from Costa.</t>
+  </si>
+  <si>
+    <t>Ventus again.</t>
+  </si>
+  <si>
+    <t>Intuitive Marcelo, that opening by Fran Beltran, made Kevin doubt just enough so that no one touched the ball.</t>
+  </si>
+  <si>
+    <t>Meha is actually the right one on the ball.</t>
+  </si>
+  <si>
+    <t>In a practically full Camp Nou.</t>
+  </si>
+  <si>
+    <t>They say he was on the list of Aurelio de Laurentiis, the president of Naples, after the sale of Gonçalo Higuain.</t>
+  </si>
+  <si>
+    <t>Penalty shout at both ends.</t>
+  </si>
+  <si>
+    <t>It's a very tight ball.</t>
+  </si>
+  <si>
+    <t>You have to say Arsenal have done well with that.</t>
+  </si>
+  <si>
+    <t>Lobotka.</t>
+  </si>
+  <si>
+    <t>First from Kacunga and last from Lukas Rupp.</t>
+  </si>
+  <si>
+    <t>Laura now in possession looking for a free kick that doesn't come.</t>
+  </si>
+  <si>
+    <t>Lowry lost track of it.</t>
+  </si>
+  <si>
+    <t>Vermaelen for Macerano.</t>
+  </si>
+  <si>
+    <t>They were incredible.</t>
+  </si>
+  <si>
+    <t>Teams that will consider those positions to be the minimum of their domestic requirements for this season again.</t>
+  </si>
+  <si>
+    <t>It was not his natural position, but he had many casualties in that demarcation.</t>
+  </si>
+  <si>
+    <t>And now the card is being shown.</t>
+  </si>
+  <si>
+    <t>Isco, little flick to the back post.</t>
+  </si>
+  <si>
+    <t>Because there are many people who want to buy an Italian star.</t>
+  </si>
+  <si>
+    <t>I think I have the statistics, and Ivanovic has scored 27 goals since August 2010.</t>
+  </si>
+  <si>
+    <t>I think he trusts a lot that he will have space and that he can kill him on the counter.</t>
+  </si>
+  <si>
+    <t>I think he's a good player, Adam Lallana.</t>
+  </si>
+  <si>
+    <t>And he gives them stability in the heart of the midfield.</t>
+  </si>
+  <si>
+    <t>Burak.</t>
+  </si>
+  <si>
+    <t>Maybe they changed their mind.</t>
+  </si>
+  <si>
+    <t>You can whistle a foul, you can not whistle a foul and therefore the VAR does not enter there.</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo's goal is repeated.</t>
+  </si>
+  <si>
+    <t>Sergi Roberto getting ready for a shot.</t>
+  </si>
+  <si>
+    <t>Aspire Cueta.</t>
+  </si>
+  <si>
+    <t>Keline.</t>
+  </si>
+  <si>
+    <t>This is what we are saying.</t>
+  </si>
+  <si>
+    <t>This is a very powerful football game that the team of André Breitenreiter offers in this early phase, but they are set for it.</t>
+  </si>
+  <si>
+    <t>Atletico Madrid scored the twelfth goal.</t>
+  </si>
+  <si>
+    <t>And he didn't just know, he scored a perfect goal.</t>
+  </si>
+  <si>
+    <t>On Cruz brings him down it'll be another free kick they'll have to be taken a few meters back.</t>
+  </si>
+  <si>
+    <t>It's a failed interception, Ronaldo has Benzema inside, can't get around Lopo.</t>
+  </si>
+  <si>
+    <t>All attacks are thrown in by the Spanish ex-world champion.</t>
+  </si>
+  <si>
+    <t>The pitch is strangely in poor condition normally early on in the season.</t>
+  </si>
+  <si>
+    <t>He saves the ball.</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo.</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1487,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1112,6 +1505,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1131,11 +1530,15 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="denoised_1_tokenized_224p_annotation" connectionId="1" xr16:uid="{635E7587-0BD4-7441-80A8-1B051F2B3EE9}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="denoised_1_tokenized_224p_annotation" connectionId="2" xr16:uid="{635E7587-0BD4-7441-80A8-1B051F2B3EE9}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="denoised_1_tokenized_224p_annotation" connectionId="2" xr16:uid="{28FAE329-83B7-BB4C-97D0-3BAFBE2A19B7}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="10_denoised_1_tokenized_224p_annotation" connectionId="1" xr16:uid="{4A66B805-C96D-3D4B-90B1-DD78F95E1CDE}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="denoised_1_tokenized_224p_annotation" connectionId="3" xr16:uid="{28FAE329-83B7-BB4C-97D0-3BAFBE2A19B7}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3187,6 +3590,1755 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2E0F6F-CB5F-E946-BB3D-A6719BC75C1A}">
+  <dimension ref="A1:H101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="21">
+      <c r="A2">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.16597222222222222</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0.17222222222222225</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="21">
+      <c r="A3">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0.24583333333333335</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21">
+      <c r="A4">
+        <v>318</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1.8749999999999999E-2</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2.7083333333333334E-2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21">
+      <c r="A5">
+        <v>341</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7">
+        <v>8.2638888888888887E-2</v>
+      </c>
+      <c r="D5" s="7">
+        <v>8.7500000000000008E-2</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="21">
+      <c r="A6">
+        <v>394</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.21319444444444444</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="21">
+      <c r="A7">
+        <v>414</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.29097222222222224</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="21">
+      <c r="A8">
+        <v>422</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.31041666666666667</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.31666666666666665</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="21">
+      <c r="A9">
+        <v>437</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.35486111111111113</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="21">
+      <c r="A10">
+        <v>491</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.51111111111111118</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="21">
+      <c r="A11">
+        <v>502</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="21">
+      <c r="A12">
+        <v>529</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.64930555555555558</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="21">
+      <c r="A13">
+        <v>607</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.8652777777777777</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0.86875000000000002</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="21">
+      <c r="A14">
+        <v>636</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.92361111111111116</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0.9277777777777777</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="21">
+      <c r="A15">
+        <v>655</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.97361111111111109</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.9868055555555556</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="21">
+      <c r="A16">
+        <v>674</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.0326388888888889</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1.0395833333333333</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="21">
+      <c r="A17">
+        <v>707</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1.1847222222222222</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1.1937499999999999</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="21">
+      <c r="A18">
+        <v>760</v>
+      </c>
+      <c r="B18" t="s">
+        <v>334</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.72777777777777775</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.73888888888888893</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="21">
+      <c r="A19">
+        <v>778</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="7">
+        <v>4.7916666666666663E-2</v>
+      </c>
+      <c r="D19" s="7">
+        <v>5.2777777777777778E-2</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="42">
+      <c r="A20">
+        <v>885</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.77013888888888893</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21">
+      <c r="A21">
+        <v>890</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.78263888888888899</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21">
+      <c r="A22">
+        <v>953</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1.6520833333333333</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1.6569444444444443</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21">
+      <c r="A23">
+        <v>955</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1.6604166666666667</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1.6659722222222222</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21">
+      <c r="A24">
+        <v>960</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1.6729166666666666</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.6763888888888889</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21">
+      <c r="A25">
+        <v>961</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1.675</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1.6777777777777778</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21">
+      <c r="A26">
+        <v>998</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1.8381944444444445</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1.8472222222222223</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21">
+      <c r="A27">
+        <v>1029</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="7">
+        <v>7.5694444444444439E-2</v>
+      </c>
+      <c r="D27" s="7">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21">
+      <c r="A28">
+        <v>1067</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="7">
+        <v>0.21805555555555556</v>
+      </c>
+      <c r="D28" s="7">
+        <v>0.22083333333333333</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21">
+      <c r="A29">
+        <v>1207</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.58819444444444446</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21">
+      <c r="A30">
+        <v>1318</v>
+      </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1.0090277777777776</v>
+      </c>
+      <c r="D30" s="6">
+        <v>1.0111111111111111</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21">
+      <c r="A31">
+        <v>1542</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1.6416666666666666</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1.6458333333333333</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21">
+      <c r="A32">
+        <v>1616</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1.8243055555555554</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1.8263888888888891</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="21">
+      <c r="A33">
+        <v>1636</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1.8694444444444445</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1.8729166666666668</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="21">
+      <c r="A34">
+        <v>1661</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.11527777777777777</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0.11875000000000001</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="21">
+      <c r="A35">
+        <v>1710</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.32083333333333336</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0.32708333333333334</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="21">
+      <c r="A36">
+        <v>1716</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.33819444444444446</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0.34375</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="21">
+      <c r="A37">
+        <v>1725</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.38125000000000003</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0.38680555555555557</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="21">
+      <c r="A38">
+        <v>1948</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1.3451388888888889</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1.3472222222222223</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="21">
+      <c r="A39">
+        <v>2125</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.14444444444444446</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="21">
+      <c r="A40">
+        <v>2130</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.15347222222222223</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.15694444444444444</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="21">
+      <c r="A41">
+        <v>2327</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1.4104166666666667</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1.4118055555555555</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="21">
+      <c r="A42">
+        <v>2362</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1.4916666666666665</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1.4958333333333333</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="21">
+      <c r="A43">
+        <v>2387</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="6">
+        <v>1.5881944444444445</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1.5895833333333333</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="42">
+      <c r="A44">
+        <v>2489</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.1986111111111111</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0.21319444444444444</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="21">
+      <c r="A45">
+        <v>2507</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.26597222222222222</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="21">
+      <c r="A46">
+        <v>2587</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.59930555555555554</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0.6069444444444444</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="21">
+      <c r="A47">
+        <v>2594</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="D47" s="7">
+        <v>0.62777777777777777</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="21">
+      <c r="A48">
+        <v>2674</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.84791666666666676</v>
+      </c>
+      <c r="D48" s="7">
+        <v>0.86944444444444446</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="21">
+      <c r="A49">
+        <v>2687</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.8979166666666667</v>
+      </c>
+      <c r="D49" s="7">
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="21">
+      <c r="A50">
+        <v>2837</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1.4749999999999999</v>
+      </c>
+      <c r="D50" s="6">
+        <v>1.4861111111111109</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="21">
+      <c r="A51">
+        <v>2916</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="6">
+        <v>1.6256944444444443</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1.6465277777777778</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="42">
+      <c r="A52">
+        <v>2938</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="6">
+        <v>1.7055555555555555</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1.7138888888888888</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="21">
+      <c r="A53">
+        <v>2990</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="D53" s="7">
+        <v>5.8333333333333327E-2</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="21">
+      <c r="A54">
+        <v>3121</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.34861111111111115</v>
+      </c>
+      <c r="D54" s="7">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="21">
+      <c r="A55">
+        <v>3201</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="D55" s="7">
+        <v>0.47500000000000003</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="21">
+      <c r="A56">
+        <v>3241</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.53194444444444444</v>
+      </c>
+      <c r="D56" s="7">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="21">
+      <c r="A57">
+        <v>3311</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="6">
+        <v>1.3645833333333333</v>
+      </c>
+      <c r="D57" s="6">
+        <v>1.3673611111111112</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="21">
+      <c r="A58">
+        <v>3428</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="6">
+        <v>1.6319444444444444</v>
+      </c>
+      <c r="D58" s="6">
+        <v>1.6354166666666667</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="21">
+      <c r="A59">
+        <v>3459</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1.7097222222222221</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1.7145833333333333</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="21">
+      <c r="A60">
+        <v>3468</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1.7249999999999999</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1.7277777777777779</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="21">
+      <c r="A61">
+        <v>3485</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1.7583333333333335</v>
+      </c>
+      <c r="D61" s="6">
+        <v>1.7618055555555554</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="21">
+      <c r="A62">
+        <v>3616</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="7">
+        <v>0.24444444444444446</v>
+      </c>
+      <c r="D62" s="7">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="21">
+      <c r="A63">
+        <v>3664</v>
+      </c>
+      <c r="B63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="7">
+        <v>0.34791666666666665</v>
+      </c>
+      <c r="D63" s="7">
+        <v>0.3520833333333333</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="21">
+      <c r="A64">
+        <v>3738</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="7">
+        <v>0.4993055555555555</v>
+      </c>
+      <c r="D64" s="7">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="21">
+      <c r="A65">
+        <v>3894</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="7">
+        <v>0.9243055555555556</v>
+      </c>
+      <c r="D65" s="7">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="21">
+      <c r="A66">
+        <v>3921</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="7">
+        <v>0.99097222222222225</v>
+      </c>
+      <c r="D66" s="7">
+        <v>0.99375000000000002</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="21">
+      <c r="A67">
+        <v>3940</v>
+      </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="6">
+        <v>1.0381944444444444</v>
+      </c>
+      <c r="D67" s="6">
+        <v>1.0430555555555556</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="21">
+      <c r="A68">
+        <v>3990</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="6">
+        <v>1.1708333333333334</v>
+      </c>
+      <c r="D68" s="6">
+        <v>1.1736111111111112</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="21">
+      <c r="A69">
+        <v>4261</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="7">
+        <v>7.013888888888889E-2</v>
+      </c>
+      <c r="D69" s="7">
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="21">
+      <c r="A70">
+        <v>4400</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="7">
+        <v>0.56111111111111112</v>
+      </c>
+      <c r="D70" s="7">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="21">
+      <c r="A71">
+        <v>4432</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="7">
+        <v>0.64722222222222225</v>
+      </c>
+      <c r="D71" s="7">
+        <v>0.65555555555555556</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="21">
+      <c r="A72">
+        <v>4440</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="7">
+        <v>0.66527777777777775</v>
+      </c>
+      <c r="D72" s="7">
+        <v>0.66875000000000007</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="21">
+      <c r="A73">
+        <v>4565</v>
+      </c>
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="6">
+        <v>1.0743055555555556</v>
+      </c>
+      <c r="D73" s="6">
+        <v>1.0777777777777777</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="21">
+      <c r="A74">
+        <v>4796</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="6">
+        <v>1.8625</v>
+      </c>
+      <c r="D74" s="6">
+        <v>1.8694444444444445</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="21">
+      <c r="A75">
+        <v>4848</v>
+      </c>
+      <c r="B75" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="7">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="D75" s="7">
+        <v>5.8333333333333327E-2</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="21">
+      <c r="A76">
+        <v>4855</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="7">
+        <v>7.0833333333333331E-2</v>
+      </c>
+      <c r="D76" s="7">
+        <v>7.7083333333333337E-2</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="21">
+      <c r="A77">
+        <v>4909</v>
+      </c>
+      <c r="B77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="7">
+        <v>0.20138888888888887</v>
+      </c>
+      <c r="D77" s="7">
+        <v>0.20486111111111113</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="21">
+      <c r="A78">
+        <v>5004</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" s="7">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D78" s="7">
+        <v>0.51388888888888895</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="21">
+      <c r="A79">
+        <v>5058</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79" s="7">
+        <v>0.66388888888888886</v>
+      </c>
+      <c r="D79" s="7">
+        <v>0.66805555555555562</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="21">
+      <c r="A80">
+        <v>5077</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" s="7">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="D80" s="7">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="21">
+      <c r="A81">
+        <v>5127</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" s="7">
+        <v>0.9458333333333333</v>
+      </c>
+      <c r="D81" s="7">
+        <v>0.96250000000000002</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="21">
+      <c r="A82">
+        <v>5149</v>
+      </c>
+      <c r="B82" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" s="6">
+        <v>1.0250000000000001</v>
+      </c>
+      <c r="D82" s="6">
+        <v>1.03125</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="21">
+      <c r="A83">
+        <v>5166</v>
+      </c>
+      <c r="B83" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" s="6">
+        <v>1.0951388888888889</v>
+      </c>
+      <c r="D83" s="6">
+        <v>1.0993055555555555</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="21">
+      <c r="A84">
+        <v>5234</v>
+      </c>
+      <c r="B84" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="6">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="D84" s="6">
+        <v>1.3375000000000001</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="21">
+      <c r="A85">
+        <v>5237</v>
+      </c>
+      <c r="B85" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="6">
+        <v>1.3388888888888888</v>
+      </c>
+      <c r="D85" s="6">
+        <v>1.3416666666666668</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="21">
+      <c r="A86">
+        <v>5301</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" s="6">
+        <v>1.5118055555555554</v>
+      </c>
+      <c r="D86" s="6">
+        <v>1.5159722222222223</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="42">
+      <c r="A87">
+        <v>5335</v>
+      </c>
+      <c r="B87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" s="6">
+        <v>1.6027777777777779</v>
+      </c>
+      <c r="D87" s="6">
+        <v>1.6118055555555555</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="21">
+      <c r="A88">
+        <v>5472</v>
+      </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="7">
+        <v>8.4027777777777771E-2</v>
+      </c>
+      <c r="D88" s="7">
+        <v>9.0277777777777776E-2</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="21">
+      <c r="A89">
+        <v>5612</v>
+      </c>
+      <c r="B89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="6">
+        <v>1.2541666666666667</v>
+      </c>
+      <c r="D89" s="6">
+        <v>1.2652777777777777</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="21">
+      <c r="A90">
+        <v>5753</v>
+      </c>
+      <c r="B90" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="7">
+        <v>0.15833333333333333</v>
+      </c>
+      <c r="D90" s="7">
+        <v>0.16111111111111112</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="21">
+      <c r="A91">
+        <v>5776</v>
+      </c>
+      <c r="B91" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="6">
+        <v>1.2347222222222223</v>
+      </c>
+      <c r="D91" s="6">
+        <v>1.2361111111111112</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="21">
+      <c r="A92">
+        <v>5793</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="7">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="D92" s="7">
+        <v>6.3888888888888884E-2</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="21">
+      <c r="A93">
+        <v>5852</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" s="7">
+        <v>0.21041666666666667</v>
+      </c>
+      <c r="D93" s="7">
+        <v>0.21597222222222223</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="21">
+      <c r="A94">
+        <v>6243</v>
+      </c>
+      <c r="B94" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="7">
+        <v>0.19375000000000001</v>
+      </c>
+      <c r="D94" s="7">
+        <v>0.19722222222222222</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="21">
+      <c r="A95">
+        <v>6331</v>
+      </c>
+      <c r="B95" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="7">
+        <v>0.40625</v>
+      </c>
+      <c r="D95" s="7">
+        <v>0.41250000000000003</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="21">
+      <c r="A96">
+        <v>6434</v>
+      </c>
+      <c r="B96" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="7">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="D96" s="7">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="21">
+      <c r="A97">
+        <v>6510</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="6">
+        <v>1.0305555555555557</v>
+      </c>
+      <c r="D97" s="6">
+        <v>1.0347222222222221</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="21">
+      <c r="A98">
+        <v>6531</v>
+      </c>
+      <c r="B98" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="6">
+        <v>1.0777777777777777</v>
+      </c>
+      <c r="D98" s="6">
+        <v>1.0833333333333333</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="42">
+      <c r="A99">
+        <v>6709</v>
+      </c>
+      <c r="B99" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="6">
+        <v>1.5895833333333333</v>
+      </c>
+      <c r="D99" s="6">
+        <v>1.6006944444444444</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="21">
+      <c r="A100">
+        <v>6739</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="6">
+        <v>1.6506944444444445</v>
+      </c>
+      <c r="D100" s="6">
+        <v>1.653472222222222</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="21">
+      <c r="A101">
+        <v>6777</v>
+      </c>
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="6">
+        <v>1.7145833333333333</v>
+      </c>
+      <c r="D101" s="6">
+        <v>1.7173611111111111</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H101">
+    <sortCondition ref="B2:B101"/>
+    <sortCondition ref="C2:C101"/>
+  </sortState>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EE851F-A761-7B43-AAB8-B9484D09B5F1}">
   <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
@@ -3311,7 +5463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="21">
+    <row r="6" spans="1:8" ht="42">
       <c r="A6">
         <v>511</v>
       </c>
@@ -3326,6 +5478,12 @@
       </c>
       <c r="E6" s="5" t="s">
         <v>170</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="21">
@@ -3344,6 +5502,9 @@
       <c r="E7" s="5" t="s">
         <v>155</v>
       </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="63">
       <c r="A8">
@@ -3361,6 +5522,15 @@
       <c r="E8" s="5" t="s">
         <v>235</v>
       </c>
+      <c r="F8" t="s">
+        <v>318</v>
+      </c>
+      <c r="G8">
+        <v>1.4</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="21">
       <c r="A9">
@@ -3378,6 +5548,9 @@
       <c r="E9" s="5" t="s">
         <v>313</v>
       </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="21">
       <c r="A10">
@@ -3395,6 +5568,9 @@
       <c r="E10" s="5" t="s">
         <v>61</v>
       </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="21">
       <c r="A11">
@@ -3412,6 +5588,9 @@
       <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="21">
       <c r="A12">
@@ -3429,6 +5608,9 @@
       <c r="E12" s="5" t="s">
         <v>115</v>
       </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="21">
       <c r="A13">
@@ -3446,6 +5628,9 @@
       <c r="E13" s="5" t="s">
         <v>191</v>
       </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="21">
       <c r="A14">
@@ -3463,6 +5648,9 @@
       <c r="E14" s="5" t="s">
         <v>103</v>
       </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="21">
       <c r="A15">
@@ -3480,6 +5668,9 @@
       <c r="E15" s="5" t="s">
         <v>176</v>
       </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="21">
       <c r="A16">
@@ -3497,8 +5688,11 @@
       <c r="E16" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="21">
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="21">
       <c r="A17">
         <v>1554</v>
       </c>
@@ -3514,8 +5708,11 @@
       <c r="E17" s="5" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="21">
+      <c r="F17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="21">
       <c r="A18">
         <v>1569</v>
       </c>
@@ -3531,8 +5728,11 @@
       <c r="E18" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="21">
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="21">
       <c r="A19">
         <v>1615</v>
       </c>
@@ -3548,8 +5748,11 @@
       <c r="E19" s="5" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="21">
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="21">
       <c r="A20">
         <v>1694</v>
       </c>
@@ -3565,8 +5768,11 @@
       <c r="E20" s="5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="21">
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="21">
       <c r="A21">
         <v>1703</v>
       </c>
@@ -3582,8 +5788,11 @@
       <c r="E21" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="21">
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="21">
       <c r="A22">
         <v>1730</v>
       </c>
@@ -3597,10 +5806,16 @@
         <v>271</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="21">
+        <v>320</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="21">
       <c r="A23">
         <v>1864</v>
       </c>
@@ -3616,8 +5831,11 @@
       <c r="E23" s="5" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="21">
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="21">
       <c r="A24">
         <v>1922</v>
       </c>
@@ -3631,10 +5849,13 @@
         <v>51</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="21">
+        <v>322</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="21">
       <c r="A25">
         <v>1934</v>
       </c>
@@ -3650,8 +5871,14 @@
       <c r="E25" s="5" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="21">
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="21">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -3667,8 +5894,11 @@
       <c r="E26" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="21">
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="21">
       <c r="A27">
         <v>2080</v>
       </c>
@@ -3684,8 +5914,11 @@
       <c r="E27" s="5" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="21">
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="21">
       <c r="A28">
         <v>2098</v>
       </c>
@@ -3701,8 +5934,11 @@
       <c r="E28" s="5" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="21">
+      <c r="F28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="21">
       <c r="A29">
         <v>2107</v>
       </c>
@@ -3718,8 +5954,11 @@
       <c r="E29" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="21">
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="21">
       <c r="A30">
         <v>2132</v>
       </c>
@@ -3735,8 +5974,11 @@
       <c r="E30" s="5" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="21">
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="21">
       <c r="A31">
         <v>2155</v>
       </c>
@@ -3752,8 +5994,11 @@
       <c r="E31" s="5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="21">
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="21">
       <c r="A32">
         <v>2323</v>
       </c>
@@ -3769,8 +6014,11 @@
       <c r="E32" s="5" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="42">
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="42">
       <c r="A33">
         <v>2576</v>
       </c>
@@ -3786,8 +6034,11 @@
       <c r="E33" s="5" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="42">
+      <c r="F33" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="42">
       <c r="A34">
         <v>2585</v>
       </c>
@@ -3803,8 +6054,11 @@
       <c r="E34" s="5" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="21">
+      <c r="F34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="21">
       <c r="A35">
         <v>2650</v>
       </c>
@@ -3820,8 +6074,11 @@
       <c r="E35" s="5" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="21">
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="21">
       <c r="A36">
         <v>2678</v>
       </c>
@@ -3837,8 +6094,11 @@
       <c r="E36" s="5" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="21">
+      <c r="F36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="21">
       <c r="A37">
         <v>2764</v>
       </c>
@@ -3854,8 +6114,11 @@
       <c r="E37" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="21">
+      <c r="F37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="21">
       <c r="A38">
         <v>2771</v>
       </c>
@@ -3871,8 +6134,11 @@
       <c r="E38" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="42">
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="42">
       <c r="A39">
         <v>2789</v>
       </c>
@@ -3888,8 +6154,11 @@
       <c r="E39" s="5" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="21">
+      <c r="F39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="21">
       <c r="A40">
         <v>2865</v>
       </c>
@@ -3905,8 +6174,11 @@
       <c r="E40" s="5" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="42">
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="42">
       <c r="A41">
         <v>2957</v>
       </c>
@@ -3922,8 +6194,11 @@
       <c r="E41" s="5" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="21">
+      <c r="F41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="21">
       <c r="A42">
         <v>3114</v>
       </c>
@@ -3939,8 +6214,11 @@
       <c r="E42" s="5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="21">
+      <c r="F42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="21">
       <c r="A43">
         <v>3121</v>
       </c>
@@ -3956,8 +6234,11 @@
       <c r="E43" s="5" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="21">
+      <c r="F43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="21">
       <c r="A44">
         <v>3231</v>
       </c>
@@ -3973,8 +6254,11 @@
       <c r="E44" s="5" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="21">
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="21">
       <c r="A45">
         <v>3257</v>
       </c>
@@ -3990,8 +6274,11 @@
       <c r="E45" s="5" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="21">
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="21">
       <c r="A46">
         <v>3290</v>
       </c>
@@ -4007,8 +6294,11 @@
       <c r="E46" s="5" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="21">
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="21">
       <c r="A47">
         <v>3312</v>
       </c>
@@ -4024,8 +6314,11 @@
       <c r="E47" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="21">
+      <c r="F47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="21">
       <c r="A48">
         <v>3381</v>
       </c>
@@ -4041,8 +6334,11 @@
       <c r="E48" s="5" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" ht="21">
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="21">
       <c r="A49">
         <v>3492</v>
       </c>
@@ -4058,8 +6354,11 @@
       <c r="E49" s="5" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="21">
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="21">
       <c r="A50">
         <v>3509</v>
       </c>
@@ -4075,8 +6374,11 @@
       <c r="E50" s="5" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" ht="21">
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="21">
       <c r="A51">
         <v>3612</v>
       </c>
@@ -4092,8 +6394,11 @@
       <c r="E51" s="5" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="21">
+      <c r="F51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="21">
       <c r="A52">
         <v>3662</v>
       </c>
@@ -4109,8 +6414,11 @@
       <c r="E52" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="21">
+      <c r="F52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="21">
       <c r="A53">
         <v>3787</v>
       </c>
@@ -4126,8 +6434,11 @@
       <c r="E53" s="5" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="21">
+      <c r="F53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="21">
       <c r="A54">
         <v>3837</v>
       </c>
@@ -4143,8 +6454,11 @@
       <c r="E54" s="5" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="21">
+      <c r="F54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="21">
       <c r="A55">
         <v>3901</v>
       </c>
@@ -4160,8 +6474,11 @@
       <c r="E55" s="5" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="21">
+      <c r="F55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="21">
       <c r="A56">
         <v>4094</v>
       </c>
@@ -4177,8 +6494,11 @@
       <c r="E56" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="21">
+      <c r="F56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="21">
       <c r="A57">
         <v>4119</v>
       </c>
@@ -4194,8 +6514,11 @@
       <c r="E57" s="5" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="21">
+      <c r="F57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="21">
       <c r="A58">
         <v>4204</v>
       </c>
@@ -4211,8 +6534,11 @@
       <c r="E58" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="21">
+      <c r="F58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="21">
       <c r="A59">
         <v>4333</v>
       </c>
@@ -4228,8 +6554,11 @@
       <c r="E59" s="5" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" ht="21">
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="21">
       <c r="A60">
         <v>4498</v>
       </c>
@@ -4245,8 +6574,11 @@
       <c r="E60" s="5" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="42">
+      <c r="F60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="42">
       <c r="A61">
         <v>4541</v>
       </c>
@@ -4262,8 +6594,14 @@
       <c r="E61" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="21">
+      <c r="F61" t="s">
+        <v>318</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="21">
       <c r="A62">
         <v>4556</v>
       </c>
@@ -4279,8 +6617,11 @@
       <c r="E62" s="5" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" ht="21">
+      <c r="F62" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="21">
       <c r="A63">
         <v>4608</v>
       </c>
@@ -4296,8 +6637,11 @@
       <c r="E63" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" ht="42">
+      <c r="F63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="42">
       <c r="A64">
         <v>4649</v>
       </c>
@@ -4313,8 +6657,11 @@
       <c r="E64" s="5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" ht="21">
+      <c r="F64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="21">
       <c r="A65">
         <v>4667</v>
       </c>
@@ -4330,8 +6677,11 @@
       <c r="E65" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="21">
+      <c r="F65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="21">
       <c r="A66">
         <v>4705</v>
       </c>
@@ -4347,8 +6697,11 @@
       <c r="E66" s="5" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" ht="21">
+      <c r="F66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="21">
       <c r="A67">
         <v>4866</v>
       </c>
@@ -4364,8 +6717,11 @@
       <c r="E67" s="5" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" ht="21">
+      <c r="F67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="21">
       <c r="A68">
         <v>4898</v>
       </c>
@@ -4381,8 +6737,11 @@
       <c r="E68" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="21">
+      <c r="F68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="21">
       <c r="A69">
         <v>5025</v>
       </c>
@@ -4398,8 +6757,11 @@
       <c r="E69" s="5" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="21">
+      <c r="F69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="21">
       <c r="A70">
         <v>5033</v>
       </c>
@@ -4415,8 +6777,11 @@
       <c r="E70" s="5" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" ht="21">
+      <c r="F70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="21">
       <c r="A71">
         <v>5058</v>
       </c>
@@ -4432,8 +6797,11 @@
       <c r="E71" s="5" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" ht="21">
+      <c r="F71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="21">
       <c r="A72">
         <v>5160</v>
       </c>
@@ -4449,8 +6817,11 @@
       <c r="E72" s="5" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" ht="21">
+      <c r="F72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="21">
       <c r="A73">
         <v>5170</v>
       </c>
@@ -4466,8 +6837,11 @@
       <c r="E73" s="5" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" ht="21">
+      <c r="F73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="21">
       <c r="A74">
         <v>5204</v>
       </c>
@@ -4481,10 +6855,13 @@
         <v>96</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="21">
+        <v>324</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="21">
       <c r="A75">
         <v>5275</v>
       </c>
@@ -4500,8 +6877,14 @@
       <c r="E75" s="5" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" ht="21">
+      <c r="F75" t="s">
+        <v>318</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="21">
       <c r="A76">
         <v>5347</v>
       </c>
@@ -4517,8 +6900,11 @@
       <c r="E76" s="5" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="21">
+      <c r="F76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="21">
       <c r="A77">
         <v>5371</v>
       </c>
@@ -4534,8 +6920,11 @@
       <c r="E77" s="5" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" ht="21">
+      <c r="F77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="21">
       <c r="A78">
         <v>5538</v>
       </c>
@@ -4551,8 +6940,11 @@
       <c r="E78" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" ht="21">
+      <c r="F78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="21">
       <c r="A79">
         <v>5640</v>
       </c>
@@ -4568,8 +6960,11 @@
       <c r="E79" s="5" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" ht="21">
+      <c r="F79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="21">
       <c r="A80">
         <v>5663</v>
       </c>
@@ -4585,8 +6980,11 @@
       <c r="E80" s="5" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="21">
+      <c r="F80" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="21">
       <c r="A81">
         <v>5666</v>
       </c>
@@ -4606,7 +7004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="21">
+    <row r="82" spans="1:8" ht="21">
       <c r="A82">
         <v>5712</v>
       </c>
@@ -4622,8 +7020,11 @@
       <c r="E82" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="21">
+      <c r="F82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="21">
       <c r="A83">
         <v>5770</v>
       </c>
@@ -4640,7 +7041,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="21">
+    <row r="84" spans="1:8" ht="21">
       <c r="A84">
         <v>5924</v>
       </c>
@@ -4656,8 +7057,14 @@
       <c r="E84" s="5" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="21">
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="21">
       <c r="A85">
         <v>5954</v>
       </c>
@@ -4673,8 +7080,11 @@
       <c r="E85" s="5" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="21">
+      <c r="F85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="21">
       <c r="A86">
         <v>5995</v>
       </c>
@@ -4690,8 +7100,11 @@
       <c r="E86" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="21">
+      <c r="F86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="21">
       <c r="A87">
         <v>6040</v>
       </c>
@@ -4707,8 +7120,14 @@
       <c r="E87" s="5" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="21">
+      <c r="F87">
+        <v>3</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="21">
       <c r="A88">
         <v>6062</v>
       </c>
@@ -4724,8 +7143,14 @@
       <c r="E88" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="21">
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="21">
       <c r="A89">
         <v>6068</v>
       </c>
@@ -4741,8 +7166,11 @@
       <c r="E89" s="5" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="21">
+      <c r="F89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="21">
       <c r="A90">
         <v>6119</v>
       </c>
@@ -4758,8 +7186,11 @@
       <c r="E90" s="5" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="21">
+      <c r="F90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="21">
       <c r="A91">
         <v>6139</v>
       </c>
@@ -4775,8 +7206,14 @@
       <c r="E91" s="5" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="21">
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="21">
       <c r="A92">
         <v>6151</v>
       </c>
@@ -4792,8 +7229,11 @@
       <c r="E92" s="5" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="21">
+      <c r="F92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="21">
       <c r="A93">
         <v>6158</v>
       </c>
@@ -4809,8 +7249,11 @@
       <c r="E93" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="21">
+      <c r="F93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="21">
       <c r="A94">
         <v>6288</v>
       </c>
@@ -4826,8 +7269,11 @@
       <c r="E94" s="5" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="21">
+      <c r="F94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="21">
       <c r="A95">
         <v>6377</v>
       </c>
@@ -4843,8 +7289,11 @@
       <c r="E95" s="5" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="21">
+      <c r="F95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="21">
       <c r="A96">
         <v>6404</v>
       </c>
@@ -4860,8 +7309,11 @@
       <c r="E96" s="5" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" ht="21">
+      <c r="F96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="21">
       <c r="A97">
         <v>6446</v>
       </c>
@@ -4877,8 +7329,11 @@
       <c r="E97" s="5" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" ht="21">
+      <c r="F97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="21">
       <c r="A98">
         <v>6559</v>
       </c>
@@ -4894,8 +7349,11 @@
       <c r="E98" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" ht="21">
+      <c r="F98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="21">
       <c r="A99">
         <v>6721</v>
       </c>
@@ -4911,8 +7369,11 @@
       <c r="E99" s="5" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" ht="21">
+      <c r="F99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="21">
       <c r="A100">
         <v>6810</v>
       </c>
@@ -4928,8 +7389,11 @@
       <c r="E100" s="5" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" ht="21">
+      <c r="F100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="21">
       <c r="A101">
         <v>6881</v>
       </c>
@@ -4944,10 +7408,14 @@
       </c>
       <c r="E101" s="5" t="s">
         <v>112</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/annotation_tool/annotation_template.xlsx
+++ b/annotation_tool/annotation_template.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/heste/workspace/sn-caption/annotation_tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC121F6F-2392-7541-93C6-496A58E39BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29306902-DA2E-B844-8155-87A5A0CD77FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14660" yWindow="-28180" windowWidth="33940" windowHeight="14020" activeTab="1" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
+    <workbookView xWindow="55000" yWindow="-9180" windowWidth="25600" windowHeight="14160" activeTab="2" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
   </bookViews>
   <sheets>
-    <sheet name="テンプレート" sheetId="4" r:id="rId1"/>
+    <sheet name="テンプレート_seed42" sheetId="4" r:id="rId1"/>
     <sheet name="テンプレート_seed10" sheetId="6" r:id="rId2"/>
-    <sheet name="moriy" sheetId="5" r:id="rId3"/>
+    <sheet name="moriy_seed42" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_10_denoised_1_tokenized_224p_annotation" localSheetId="1">テンプレート_seed10!$A$1:$H$101</definedName>
-    <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="2">moriy!$A$1:$H$101</definedName>
-    <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="0">テンプレート!$A$1:$H$101</definedName>
+    <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="2">moriy_seed42!$A$1:$H$101</definedName>
+    <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="0">テンプレート_seed42!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="435">
   <si>
     <t>id</t>
   </si>
@@ -1112,16 +1112,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>付加的情報混じりの感想</t>
-    <rPh sb="0" eb="5">
-      <t xml:space="preserve">フカテキジョウホウ </t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t xml:space="preserve">マジリノカンソウ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>迷</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1140,309 +1130,393 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ちょいノイズ？</t>
+    <t>Now a idea.</t>
+  </si>
+  <si>
+    <t>He's smart because he's a fake.</t>
+  </si>
+  <si>
+    <t>It's Alaba and Alonso at the heart of that by in defence so it is very much unfamiliar looking defensive line for the home side.</t>
+  </si>
+  <si>
+    <t>When we say holding in the box, we're not talking about a foul now.</t>
+  </si>
+  <si>
+    <t>2015-02-15 - 14-30 AC Milan 1 - 1 Empoli</t>
+  </si>
+  <si>
+    <t>...Menes really is the... ...inspiration for Milan... ...at the moment.</t>
+  </si>
+  <si>
+    <t>Dani Alves is trying to score.</t>
+  </si>
+  <si>
+    <t>Alexander has a problem with the ball.</t>
+  </si>
+  <si>
+    <t>He became much coveted after his time at Southampton, which began here.</t>
+  </si>
+  <si>
+    <t>Mkhmedi.</t>
+  </si>
+  <si>
+    <t>The number 19 Ivan Cavallero.</t>
+  </si>
+  <si>
+    <t>Ronaldo got a hat-trick that day as I mentioned.</t>
+  </si>
+  <si>
+    <t>Marcelo wanted to leave first for Kroos, he gives it directly to the rival.</t>
+  </si>
+  <si>
+    <t>Now the counter-attack.</t>
+  </si>
+  <si>
+    <t>He's been controlling all these things.</t>
+  </si>
+  <si>
+    <t>Kjezo again.</t>
+  </si>
+  <si>
+    <t>Paderborn from the beginning with a clear defense concept.</t>
+  </si>
+  <si>
+    <t>Koke.</t>
+  </si>
+  <si>
+    <t>He shot from a distance.</t>
+  </si>
+  <si>
+    <t>The problem for FC Barcelona is Alventosa's presence.</t>
+  </si>
+  <si>
+    <t>Calcio is returning, which, I think, all fans of the series are very happy about.</t>
+  </si>
+  <si>
+    <t>Hey!</t>
+  </si>
+  <si>
+    <t>Hasn't yet been a break in play.</t>
+  </si>
+  <si>
+    <t>Dani Alves is playing with a traditional Juventus' style.</t>
+  </si>
+  <si>
+    <t>I don't think so.</t>
+  </si>
+  <si>
+    <t>The Zinedine Zidane team are trying to get the ball out, Toni Kroos is looking for it, it's a bad pass.</t>
+  </si>
+  <si>
+    <t>Now Hulk up.</t>
+  </si>
+  <si>
+    <t>And then the non-rule climbing handball.</t>
+  </si>
+  <si>
+    <t>Vidal.</t>
+  </si>
+  <si>
+    <t>Does the little pass inside.</t>
+  </si>
+  <si>
+    <t>Depor will come out obviously looking to defend their goal especially over the first 20 minutes or so.</t>
+  </si>
+  <si>
+    <t>There was no flag.</t>
+  </si>
+  <si>
+    <t>Chelsea in those wide areas.</t>
+  </si>
+  <si>
+    <t>Everything you can win by 1-0 is always very dangerous.</t>
+  </si>
+  <si>
+    <t>The player of the German national team scores the first Juventus ball in the new season.</t>
+  </si>
+  <si>
+    <t>So good start here for the Galicians.</t>
+  </si>
+  <si>
+    <t>Rakitic.</t>
+  </si>
+  <si>
+    <t>Another long ball.</t>
+  </si>
+  <si>
+    <t>Mario Götze is left to Stefan Ilsenker.</t>
+  </si>
+  <si>
+    <t>Nacho outside to the Brazilian left back.</t>
+  </si>
+  <si>
+    <t>Good wall from Bernardeschi.</t>
+  </si>
+  <si>
+    <t>Shaquille has failed.</t>
+  </si>
+  <si>
+    <t>Burak is turning.</t>
+  </si>
+  <si>
+    <t>He scored a yellow-red goal in Lviv.</t>
+  </si>
+  <si>
+    <t>Ribéry, quickly with Lewandowski.</t>
+  </si>
+  <si>
+    <t>He shoots the header.</t>
+  </si>
+  <si>
+    <t>I think he's capable of it.</t>
+  </si>
+  <si>
+    <t>That's why the great good of European football covered his signature.</t>
+  </si>
+  <si>
+    <t>Trapp!</t>
+  </si>
+  <si>
+    <t>But I think everybody knew Cristiano Ronaldo was going to go for goal from that position.</t>
+  </si>
+  <si>
+    <t>It's going to move.</t>
+  </si>
+  <si>
+    <t>And got themselves right back in the game.</t>
+  </si>
+  <si>
+    <t>Although it's just going to beat Marquinhos.</t>
+  </si>
+  <si>
+    <t>Chalhanoglu helps it on towards Kiesling.</t>
+  </si>
+  <si>
+    <t>I must say that they are taking advantage of the change of rules.</t>
+  </si>
+  <si>
+    <t>This is not good for PSG.</t>
+  </si>
+  <si>
+    <t>The ball continues to be on the left side.</t>
+  </si>
+  <si>
+    <t>Hilbert under pressure from Costa.</t>
+  </si>
+  <si>
+    <t>Ventus again.</t>
+  </si>
+  <si>
+    <t>Intuitive Marcelo, that opening by Fran Beltran, made Kevin doubt just enough so that no one touched the ball.</t>
+  </si>
+  <si>
+    <t>Meha is actually the right one on the ball.</t>
+  </si>
+  <si>
+    <t>In a practically full Camp Nou.</t>
+  </si>
+  <si>
+    <t>They say he was on the list of Aurelio de Laurentiis, the president of Naples, after the sale of Gonçalo Higuain.</t>
+  </si>
+  <si>
+    <t>Penalty shout at both ends.</t>
+  </si>
+  <si>
+    <t>It's a very tight ball.</t>
+  </si>
+  <si>
+    <t>You have to say Arsenal have done well with that.</t>
+  </si>
+  <si>
+    <t>Lobotka.</t>
+  </si>
+  <si>
+    <t>First from Kacunga and last from Lukas Rupp.</t>
+  </si>
+  <si>
+    <t>Laura now in possession looking for a free kick that doesn't come.</t>
+  </si>
+  <si>
+    <t>Lowry lost track of it.</t>
+  </si>
+  <si>
+    <t>Vermaelen for Macerano.</t>
+  </si>
+  <si>
+    <t>They were incredible.</t>
+  </si>
+  <si>
+    <t>Teams that will consider those positions to be the minimum of their domestic requirements for this season again.</t>
+  </si>
+  <si>
+    <t>It was not his natural position, but he had many casualties in that demarcation.</t>
+  </si>
+  <si>
+    <t>And now the card is being shown.</t>
+  </si>
+  <si>
+    <t>Isco, little flick to the back post.</t>
+  </si>
+  <si>
+    <t>Because there are many people who want to buy an Italian star.</t>
+  </si>
+  <si>
+    <t>I think I have the statistics, and Ivanovic has scored 27 goals since August 2010.</t>
+  </si>
+  <si>
+    <t>I think he trusts a lot that he will have space and that he can kill him on the counter.</t>
+  </si>
+  <si>
+    <t>I think he's a good player, Adam Lallana.</t>
+  </si>
+  <si>
+    <t>And he gives them stability in the heart of the midfield.</t>
+  </si>
+  <si>
+    <t>Burak.</t>
+  </si>
+  <si>
+    <t>Maybe they changed their mind.</t>
+  </si>
+  <si>
+    <t>You can whistle a foul, you can not whistle a foul and therefore the VAR does not enter there.</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo's goal is repeated.</t>
+  </si>
+  <si>
+    <t>Sergi Roberto getting ready for a shot.</t>
+  </si>
+  <si>
+    <t>Aspire Cueta.</t>
+  </si>
+  <si>
+    <t>Keline.</t>
+  </si>
+  <si>
+    <t>This is what we are saying.</t>
+  </si>
+  <si>
+    <t>This is a very powerful football game that the team of André Breitenreiter offers in this early phase, but they are set for it.</t>
+  </si>
+  <si>
+    <t>Atletico Madrid scored the twelfth goal.</t>
+  </si>
+  <si>
+    <t>And he didn't just know, he scored a perfect goal.</t>
+  </si>
+  <si>
+    <t>On Cruz brings him down it'll be another free kick they'll have to be taken a few meters back.</t>
+  </si>
+  <si>
+    <t>It's a failed interception, Ronaldo has Benzema inside, can't get around Lopo.</t>
+  </si>
+  <si>
+    <t>All attacks are thrown in by the Spanish ex-world champion.</t>
+  </si>
+  <si>
+    <t>The pitch is strangely in poor condition normally early on in the season.</t>
+  </si>
+  <si>
+    <t>He saves the ball.</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo.</t>
+  </si>
+  <si>
+    <t>迷。付加的情報混じりの感想</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">マヨッタ </t>
+    </rPh>
+    <rPh sb="2" eb="7">
+      <t xml:space="preserve">フカテキジョウホウ </t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">マジリノカンソウ </t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Now a idea.</t>
-  </si>
-  <si>
-    <t>He's smart because he's a fake.</t>
-  </si>
-  <si>
-    <t>It's Alaba and Alonso at the heart of that by in defence so it is very much unfamiliar looking defensive line for the home side.</t>
-  </si>
-  <si>
-    <t>When we say holding in the box, we're not talking about a foul now.</t>
-  </si>
-  <si>
-    <t>2015-02-15 - 14-30 AC Milan 1 - 1 Empoli</t>
-  </si>
-  <si>
-    <t>...Menes really is the... ...inspiration for Milan... ...at the moment.</t>
-  </si>
-  <si>
-    <t>Dani Alves is trying to score.</t>
-  </si>
-  <si>
-    <t>Alexander has a problem with the ball.</t>
-  </si>
-  <si>
-    <t>He became much coveted after his time at Southampton, which began here.</t>
-  </si>
-  <si>
-    <t>Mkhmedi.</t>
-  </si>
-  <si>
-    <t>The number 19 Ivan Cavallero.</t>
-  </si>
-  <si>
-    <t>Ronaldo got a hat-trick that day as I mentioned.</t>
-  </si>
-  <si>
-    <t>Marcelo wanted to leave first for Kroos, he gives it directly to the rival.</t>
-  </si>
-  <si>
-    <t>Now the counter-attack.</t>
-  </si>
-  <si>
-    <t>He's been controlling all these things.</t>
-  </si>
-  <si>
-    <t>Kjezo again.</t>
-  </si>
-  <si>
-    <t>Paderborn from the beginning with a clear defense concept.</t>
-  </si>
-  <si>
-    <t>Koke.</t>
-  </si>
-  <si>
-    <t>He shot from a distance.</t>
-  </si>
-  <si>
-    <t>The problem for FC Barcelona is Alventosa's presence.</t>
-  </si>
-  <si>
-    <t>Calcio is returning, which, I think, all fans of the series are very happy about.</t>
-  </si>
-  <si>
-    <t>Hey!</t>
-  </si>
-  <si>
-    <t>Hasn't yet been a break in play.</t>
-  </si>
-  <si>
-    <t>Dani Alves is playing with a traditional Juventus' style.</t>
-  </si>
-  <si>
-    <t>I don't think so.</t>
-  </si>
-  <si>
-    <t>The Zinedine Zidane team are trying to get the ball out, Toni Kroos is looking for it, it's a bad pass.</t>
-  </si>
-  <si>
-    <t>Now Hulk up.</t>
-  </si>
-  <si>
-    <t>And then the non-rule climbing handball.</t>
-  </si>
-  <si>
-    <t>Vidal.</t>
-  </si>
-  <si>
-    <t>Does the little pass inside.</t>
-  </si>
-  <si>
-    <t>Depor will come out obviously looking to defend their goal especially over the first 20 minutes or so.</t>
-  </si>
-  <si>
-    <t>There was no flag.</t>
-  </si>
-  <si>
-    <t>Chelsea in those wide areas.</t>
-  </si>
-  <si>
-    <t>Everything you can win by 1-0 is always very dangerous.</t>
-  </si>
-  <si>
-    <t>The player of the German national team scores the first Juventus ball in the new season.</t>
-  </si>
-  <si>
-    <t>So good start here for the Galicians.</t>
-  </si>
-  <si>
-    <t>Rakitic.</t>
-  </si>
-  <si>
-    <t>Another long ball.</t>
-  </si>
-  <si>
-    <t>Mario Götze is left to Stefan Ilsenker.</t>
-  </si>
-  <si>
-    <t>Nacho outside to the Brazilian left back.</t>
-  </si>
-  <si>
-    <t>Good wall from Bernardeschi.</t>
-  </si>
-  <si>
-    <t>Shaquille has failed.</t>
-  </si>
-  <si>
-    <t>Burak is turning.</t>
-  </si>
-  <si>
-    <t>He scored a yellow-red goal in Lviv.</t>
-  </si>
-  <si>
-    <t>Ribéry, quickly with Lewandowski.</t>
-  </si>
-  <si>
-    <t>He shoots the header.</t>
-  </si>
-  <si>
-    <t>I think he's capable of it.</t>
-  </si>
-  <si>
-    <t>That's why the great good of European football covered his signature.</t>
-  </si>
-  <si>
-    <t>Trapp!</t>
-  </si>
-  <si>
-    <t>But I think everybody knew Cristiano Ronaldo was going to go for goal from that position.</t>
-  </si>
-  <si>
-    <t>It's going to move.</t>
-  </si>
-  <si>
-    <t>And got themselves right back in the game.</t>
-  </si>
-  <si>
-    <t>Although it's just going to beat Marquinhos.</t>
-  </si>
-  <si>
-    <t>Chalhanoglu helps it on towards Kiesling.</t>
-  </si>
-  <si>
-    <t>I must say that they are taking advantage of the change of rules.</t>
-  </si>
-  <si>
-    <t>This is not good for PSG.</t>
-  </si>
-  <si>
-    <t>The ball continues to be on the left side.</t>
-  </si>
-  <si>
-    <t>Hilbert under pressure from Costa.</t>
-  </si>
-  <si>
-    <t>Ventus again.</t>
-  </si>
-  <si>
-    <t>Intuitive Marcelo, that opening by Fran Beltran, made Kevin doubt just enough so that no one touched the ball.</t>
-  </si>
-  <si>
-    <t>Meha is actually the right one on the ball.</t>
-  </si>
-  <si>
-    <t>In a practically full Camp Nou.</t>
-  </si>
-  <si>
-    <t>They say he was on the list of Aurelio de Laurentiis, the president of Naples, after the sale of Gonçalo Higuain.</t>
-  </si>
-  <si>
-    <t>Penalty shout at both ends.</t>
-  </si>
-  <si>
-    <t>It's a very tight ball.</t>
-  </si>
-  <si>
-    <t>You have to say Arsenal have done well with that.</t>
-  </si>
-  <si>
-    <t>Lobotka.</t>
-  </si>
-  <si>
-    <t>First from Kacunga and last from Lukas Rupp.</t>
-  </si>
-  <si>
-    <t>Laura now in possession looking for a free kick that doesn't come.</t>
-  </si>
-  <si>
-    <t>Lowry lost track of it.</t>
-  </si>
-  <si>
-    <t>Vermaelen for Macerano.</t>
-  </si>
-  <si>
-    <t>They were incredible.</t>
-  </si>
-  <si>
-    <t>Teams that will consider those positions to be the minimum of their domestic requirements for this season again.</t>
-  </si>
-  <si>
-    <t>It was not his natural position, but he had many casualties in that demarcation.</t>
-  </si>
-  <si>
-    <t>And now the card is being shown.</t>
-  </si>
-  <si>
-    <t>Isco, little flick to the back post.</t>
-  </si>
-  <si>
-    <t>Because there are many people who want to buy an Italian star.</t>
-  </si>
-  <si>
-    <t>I think I have the statistics, and Ivanovic has scored 27 goals since August 2010.</t>
-  </si>
-  <si>
-    <t>I think he trusts a lot that he will have space and that he can kill him on the counter.</t>
-  </si>
-  <si>
-    <t>I think he's a good player, Adam Lallana.</t>
-  </si>
-  <si>
-    <t>And he gives them stability in the heart of the midfield.</t>
-  </si>
-  <si>
-    <t>Burak.</t>
-  </si>
-  <si>
-    <t>Maybe they changed their mind.</t>
-  </si>
-  <si>
-    <t>You can whistle a foul, you can not whistle a foul and therefore the VAR does not enter there.</t>
-  </si>
-  <si>
-    <t>Cristiano Ronaldo's goal is repeated.</t>
-  </si>
-  <si>
-    <t>Sergi Roberto getting ready for a shot.</t>
-  </si>
-  <si>
-    <t>Aspire Cueta.</t>
-  </si>
-  <si>
-    <t>Keline.</t>
-  </si>
-  <si>
-    <t>This is what we are saying.</t>
-  </si>
-  <si>
-    <t>This is a very powerful football game that the team of André Breitenreiter offers in this early phase, but they are set for it.</t>
-  </si>
-  <si>
-    <t>Atletico Madrid scored the twelfth goal.</t>
-  </si>
-  <si>
-    <t>And he didn't just know, he scored a perfect goal.</t>
-  </si>
-  <si>
-    <t>On Cruz brings him down it'll be another free kick they'll have to be taken a few meters back.</t>
-  </si>
-  <si>
-    <t>It's a failed interception, Ronaldo has Benzema inside, can't get around Lopo.</t>
-  </si>
-  <si>
-    <t>All attacks are thrown in by the Spanish ex-world champion.</t>
-  </si>
-  <si>
-    <t>The pitch is strangely in poor condition normally early on in the season.</t>
-  </si>
-  <si>
-    <t>He saves the ball.</t>
-  </si>
-  <si>
-    <t>Cristiano Ronaldo.</t>
+    <r>
+      <t xml:space="preserve">We are watching again Atletico Madrid </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In 2010</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In UEFA European League　（最近洗練されていたアトレティコだが、この試合は昔のようなよくない調子、という意味で捉えた）</t>
+    </r>
+    <rPh sb="71" eb="75">
+      <t xml:space="preserve">サイキンセンレン </t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t xml:space="preserve">ムカシノヨウナ </t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t xml:space="preserve">チョウシ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファールシーンで、削られた側がうまくいなしている状況</t>
+    <rPh sb="9" eb="10">
+      <t xml:space="preserve">ケズラレタガワ </t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t xml:space="preserve">ジョウキョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完全な文章ではない</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">カンゼン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>What an impression he's made on Bayern and what a remarkable achievement it would be if he could produce that unprecedented fourth consecutive Bundesliga title.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2016-08-14 - 18-00 Arsenal 3 - 4 Liverpool</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sneijder.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2015-08-29 - 19-30 Bayern Munich 3 - 0 Bayer Leverkusen</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1455,6 +1529,15 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -3642,7 +3725,7 @@
         <v>0.17222222222222225</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="21">
@@ -3659,7 +3742,7 @@
         <v>0.25</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21">
@@ -3676,7 +3759,7 @@
         <v>2.7083333333333334E-2</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21">
@@ -3693,7 +3776,7 @@
         <v>8.7500000000000008E-2</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="21">
@@ -3710,7 +3793,7 @@
         <v>0.21319444444444444</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="21">
@@ -3727,7 +3810,7 @@
         <v>0.29097222222222224</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="21">
@@ -3744,7 +3827,7 @@
         <v>0.31666666666666665</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="21">
@@ -3761,7 +3844,7 @@
         <v>0.35486111111111113</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="21">
@@ -3778,7 +3861,7 @@
         <v>0.51111111111111118</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="21">
@@ -3795,7 +3878,7 @@
         <v>0.53055555555555556</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="21">
@@ -3812,7 +3895,7 @@
         <v>0.64930555555555558</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="21">
@@ -3829,7 +3912,7 @@
         <v>0.86875000000000002</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="21">
@@ -3846,7 +3929,7 @@
         <v>0.9277777777777777</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21">
@@ -3863,7 +3946,7 @@
         <v>0.9868055555555556</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="21">
@@ -3880,7 +3963,7 @@
         <v>1.0395833333333333</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="21">
@@ -3897,7 +3980,7 @@
         <v>1.1937499999999999</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="21">
@@ -3905,7 +3988,7 @@
         <v>760</v>
       </c>
       <c r="B18" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C18" s="7">
         <v>0.72777777777777775</v>
@@ -3914,7 +3997,7 @@
         <v>0.73888888888888893</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="21">
@@ -3931,7 +4014,7 @@
         <v>5.2777777777777778E-2</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="42">
@@ -3948,7 +4031,7 @@
         <v>0.77013888888888893</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="21">
@@ -3965,7 +4048,7 @@
         <v>0.79236111111111107</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="21">
@@ -3982,7 +4065,7 @@
         <v>1.6569444444444443</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="21">
@@ -3999,7 +4082,7 @@
         <v>1.6659722222222222</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="21">
@@ -4016,7 +4099,7 @@
         <v>1.6763888888888889</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="21">
@@ -4033,7 +4116,7 @@
         <v>1.6777777777777778</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="21">
@@ -4050,7 +4133,7 @@
         <v>1.8472222222222223</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="21">
@@ -4067,7 +4150,7 @@
         <v>8.1250000000000003E-2</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="21">
@@ -4084,7 +4167,7 @@
         <v>0.22083333333333333</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="21">
@@ -4101,7 +4184,7 @@
         <v>0.59166666666666667</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="21">
@@ -4118,7 +4201,7 @@
         <v>1.0111111111111111</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="21">
@@ -4135,7 +4218,7 @@
         <v>1.6458333333333333</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="21">
@@ -4152,7 +4235,7 @@
         <v>1.8263888888888891</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="21">
@@ -4169,7 +4252,7 @@
         <v>1.8729166666666668</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="21">
@@ -4186,7 +4269,7 @@
         <v>0.11875000000000001</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="21">
@@ -4203,7 +4286,7 @@
         <v>0.32708333333333334</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="21">
@@ -4220,7 +4303,7 @@
         <v>0.34375</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="21">
@@ -4237,7 +4320,7 @@
         <v>0.38680555555555557</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="21">
@@ -4254,7 +4337,7 @@
         <v>1.3472222222222223</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="21">
@@ -4271,7 +4354,7 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="21">
@@ -4288,7 +4371,7 @@
         <v>0.15694444444444444</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="21">
@@ -4305,7 +4388,7 @@
         <v>1.4118055555555555</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="21">
@@ -4322,7 +4405,7 @@
         <v>1.4958333333333333</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="21">
@@ -4339,7 +4422,7 @@
         <v>1.5895833333333333</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="42">
@@ -4356,7 +4439,7 @@
         <v>0.21319444444444444</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="21">
@@ -4373,7 +4456,7 @@
         <v>0.2722222222222222</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="21">
@@ -4390,7 +4473,7 @@
         <v>0.6069444444444444</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="21">
@@ -4407,7 +4490,7 @@
         <v>0.62777777777777777</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="21">
@@ -4424,7 +4507,7 @@
         <v>0.86944444444444446</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="21">
@@ -4441,7 +4524,7 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="21">
@@ -4458,7 +4541,7 @@
         <v>1.4861111111111109</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="21">
@@ -4475,7 +4558,7 @@
         <v>1.6465277777777778</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="42">
@@ -4492,7 +4575,7 @@
         <v>1.7138888888888888</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="21">
@@ -4509,7 +4592,7 @@
         <v>5.8333333333333327E-2</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="21">
@@ -4543,7 +4626,7 @@
         <v>0.47500000000000003</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="21">
@@ -4560,7 +4643,7 @@
         <v>0.53333333333333333</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="21">
@@ -4577,7 +4660,7 @@
         <v>1.3673611111111112</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="21">
@@ -4594,7 +4677,7 @@
         <v>1.6354166666666667</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="21">
@@ -4611,7 +4694,7 @@
         <v>1.7145833333333333</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="21">
@@ -4628,7 +4711,7 @@
         <v>1.7277777777777779</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="21">
@@ -4645,7 +4728,7 @@
         <v>1.7618055555555554</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="21">
@@ -4679,7 +4762,7 @@
         <v>0.3520833333333333</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="21">
@@ -4696,7 +4779,7 @@
         <v>0.50138888888888888</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="21">
@@ -4713,7 +4796,7 @@
         <v>0.92708333333333337</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="21">
@@ -4730,7 +4813,7 @@
         <v>0.99375000000000002</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="21">
@@ -4747,7 +4830,7 @@
         <v>1.0430555555555556</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="21">
@@ -4764,7 +4847,7 @@
         <v>1.1736111111111112</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="21">
@@ -4781,7 +4864,7 @@
         <v>7.9166666666666663E-2</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="21">
@@ -4798,7 +4881,7 @@
         <v>0.56319444444444444</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="21">
@@ -4815,7 +4898,7 @@
         <v>0.65555555555555556</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="21">
@@ -4832,7 +4915,7 @@
         <v>0.66875000000000007</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="21">
@@ -4849,7 +4932,7 @@
         <v>1.0777777777777777</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="21">
@@ -4866,7 +4949,7 @@
         <v>1.8694444444444445</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="21">
@@ -4883,7 +4966,7 @@
         <v>5.8333333333333327E-2</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="21">
@@ -4900,7 +4983,7 @@
         <v>7.7083333333333337E-2</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="21">
@@ -4917,7 +5000,7 @@
         <v>0.20486111111111113</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="21">
@@ -4934,7 +5017,7 @@
         <v>0.51388888888888895</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="21">
@@ -4968,7 +5051,7 @@
         <v>0.72222222222222221</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="21">
@@ -4985,7 +5068,7 @@
         <v>0.96250000000000002</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="21">
@@ -5002,7 +5085,7 @@
         <v>1.03125</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="21">
@@ -5019,7 +5102,7 @@
         <v>1.0993055555555555</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="21">
@@ -5036,7 +5119,7 @@
         <v>1.3375000000000001</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="21">
@@ -5053,7 +5136,7 @@
         <v>1.3416666666666668</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="21">
@@ -5070,7 +5153,7 @@
         <v>1.5159722222222223</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="42">
@@ -5087,7 +5170,7 @@
         <v>1.6118055555555555</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="21">
@@ -5104,7 +5187,7 @@
         <v>9.0277777777777776E-2</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="21">
@@ -5121,7 +5204,7 @@
         <v>1.2652777777777777</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="21">
@@ -5138,7 +5221,7 @@
         <v>0.16111111111111112</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="21">
@@ -5155,7 +5238,7 @@
         <v>1.2361111111111112</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="21">
@@ -5172,7 +5255,7 @@
         <v>6.3888888888888884E-2</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="21">
@@ -5189,7 +5272,7 @@
         <v>0.21597222222222223</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="21">
@@ -5206,7 +5289,7 @@
         <v>0.19722222222222222</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="21">
@@ -5223,7 +5306,7 @@
         <v>0.41250000000000003</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="21">
@@ -5240,7 +5323,7 @@
         <v>0.76736111111111116</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="21">
@@ -5257,7 +5340,7 @@
         <v>1.0347222222222221</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="21">
@@ -5274,7 +5357,7 @@
         <v>1.0833333333333333</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="42">
@@ -5291,7 +5374,7 @@
         <v>1.6006944444444444</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="21">
@@ -5308,7 +5391,7 @@
         <v>1.653472222222222</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="21">
@@ -5325,7 +5408,7 @@
         <v>1.7173611111111111</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -5347,8 +5430,9 @@
     <col min="2" max="2" width="53.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="80.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.85546875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" customWidth="1"/>
+    <col min="8" max="8" width="44.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="21">
@@ -5875,7 +5959,7 @@
         <v>2</v>
       </c>
       <c r="G25">
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="21">
@@ -6018,7 +6102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="42">
+    <row r="33" spans="1:7" ht="42">
       <c r="A33">
         <v>2576</v>
       </c>
@@ -6032,13 +6116,16 @@
         <v>300</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>301</v>
+        <v>431</v>
       </c>
       <c r="F33" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="42">
+      <c r="G33">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="42">
       <c r="A34">
         <v>2585</v>
       </c>
@@ -6057,8 +6144,11 @@
       <c r="F34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="21">
+      <c r="G34">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="21">
       <c r="A35">
         <v>2650</v>
       </c>
@@ -6078,7 +6168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="21">
+    <row r="36" spans="1:7" ht="21">
       <c r="A36">
         <v>2678</v>
       </c>
@@ -6098,7 +6188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="21">
+    <row r="37" spans="1:7" ht="21">
       <c r="A37">
         <v>2764</v>
       </c>
@@ -6117,8 +6207,11 @@
       <c r="F37">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="21">
+      <c r="G37">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="21">
       <c r="A38">
         <v>2771</v>
       </c>
@@ -6138,7 +6231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="42">
+    <row r="39" spans="1:7" ht="42">
       <c r="A39">
         <v>2789</v>
       </c>
@@ -6157,13 +6250,16 @@
       <c r="F39">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="21">
+      <c r="G39">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="21">
       <c r="A40">
         <v>2865</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>434</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>148</v>
@@ -6177,8 +6273,11 @@
       <c r="F40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="42">
+      <c r="G40">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="42">
       <c r="A41">
         <v>2957</v>
       </c>
@@ -6198,7 +6297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="21">
+    <row r="42" spans="1:7" ht="21">
       <c r="A42">
         <v>3114</v>
       </c>
@@ -6218,7 +6317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="21">
+    <row r="43" spans="1:7" ht="21">
       <c r="A43">
         <v>3121</v>
       </c>
@@ -6238,7 +6337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="21">
+    <row r="44" spans="1:7" ht="21">
       <c r="A44">
         <v>3231</v>
       </c>
@@ -6258,7 +6357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="21">
+    <row r="45" spans="1:7" ht="21">
       <c r="A45">
         <v>3257</v>
       </c>
@@ -6278,7 +6377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="21">
+    <row r="46" spans="1:7" ht="21">
       <c r="A46">
         <v>3290</v>
       </c>
@@ -6298,7 +6397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="21">
+    <row r="47" spans="1:7" ht="21">
       <c r="A47">
         <v>3312</v>
       </c>
@@ -6318,7 +6417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="21">
+    <row r="48" spans="1:7" ht="21">
       <c r="A48">
         <v>3381</v>
       </c>
@@ -6437,6 +6536,9 @@
       <c r="F53">
         <v>2</v>
       </c>
+      <c r="G53">
+        <v>2.2999999999999998</v>
+      </c>
     </row>
     <row r="54" spans="1:8" ht="21">
       <c r="A54">
@@ -6498,7 +6600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="21">
+    <row r="57" spans="1:8" ht="84">
       <c r="A57">
         <v>4119</v>
       </c>
@@ -6515,7 +6617,10 @@
         <v>226</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="21">
@@ -6532,7 +6637,7 @@
         <v>66</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>67</v>
+        <v>433</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -6597,6 +6702,9 @@
       <c r="F61" t="s">
         <v>318</v>
       </c>
+      <c r="G61">
+        <v>3.3</v>
+      </c>
       <c r="H61" s="5" t="s">
         <v>323</v>
       </c>
@@ -6606,7 +6714,7 @@
         <v>4556</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>432</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>118</v>
@@ -6619,6 +6727,9 @@
       </c>
       <c r="F62" t="s">
         <v>318</v>
+      </c>
+      <c r="G62">
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="21">
@@ -6640,6 +6751,9 @@
       <c r="F63">
         <v>2</v>
       </c>
+      <c r="G63">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
     <row r="64" spans="1:8" ht="42">
       <c r="A64">
@@ -6780,6 +6894,9 @@
       <c r="F70">
         <v>2</v>
       </c>
+      <c r="G70">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="71" spans="1:8" ht="21">
       <c r="A71">
@@ -6877,11 +6994,11 @@
       <c r="E75" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F75" t="s">
-        <v>318</v>
+      <c r="F75">
+        <v>3</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="21">
@@ -6923,6 +7040,9 @@
       <c r="F77">
         <v>2</v>
       </c>
+      <c r="G77">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="78" spans="1:8" ht="21">
       <c r="A78">
@@ -6964,7 +7084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="21">
+    <row r="80" spans="1:8" ht="42">
       <c r="A80">
         <v>5663</v>
       </c>
@@ -6981,7 +7101,10 @@
         <v>197</v>
       </c>
       <c r="F80" t="s">
-        <v>318</v>
+        <v>428</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="21">
@@ -7040,6 +7163,9 @@
       <c r="E83" s="5" t="s">
         <v>269</v>
       </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
     </row>
     <row r="84" spans="1:8" ht="21">
       <c r="A84">
@@ -7061,7 +7187,7 @@
         <v>3</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="21">
@@ -7124,7 +7250,7 @@
         <v>3</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="21">
@@ -7147,7 +7273,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="21">
@@ -7189,6 +7315,9 @@
       <c r="F90">
         <v>2</v>
       </c>
+      <c r="G90">
+        <v>2.2999999999999998</v>
+      </c>
     </row>
     <row r="91" spans="1:8" ht="21">
       <c r="A91">
@@ -7210,7 +7339,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>329</v>
+        <v>430</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="21">

--- a/annotation_tool/annotation_template.xlsx
+++ b/annotation_tool/annotation_template.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/heste/workspace/sn-caption/annotation_tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29306902-DA2E-B844-8155-87A5A0CD77FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC213EB-103A-F94C-9B0A-F02FED668E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="55000" yWindow="-9180" windowWidth="25600" windowHeight="14160" activeTab="2" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
+    <workbookView xWindow="31180" yWindow="4740" windowWidth="25600" windowHeight="14140" activeTab="3" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート_seed42" sheetId="4" r:id="rId1"/>
     <sheet name="テンプレート_seed10" sheetId="6" r:id="rId2"/>
     <sheet name="moriy_seed42" sheetId="5" r:id="rId3"/>
+    <sheet name="moriy_bin_seed42" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_10_denoised_1_tokenized_224p_annotation" localSheetId="1">テンプレート_seed10!$A$1:$H$101</definedName>
+    <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="3">moriy_bin_seed42!$A$1:$I$101</definedName>
     <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="2">moriy_seed42!$A$1:$H$101</definedName>
     <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="0">テンプレート_seed42!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -87,11 +88,25 @@
       </textFields>
     </textPr>
   </connection>
+  <connection id="4" xr16:uid="{07CCAF68-FEFA-224A-9FB8-A656BAEF5036}" name="denoised_1_tokenized_224p_annotation111" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="65001" sourceFile="/Users/heste/workspace/sn-caption/data/denoised_1_tokenized_224p_annotation.csv" tab="0" comma="1">
+      <textFields count="8">
+        <textField/>
+        <textField/>
+        <textField type="text"/>
+        <textField type="text"/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="438">
   <si>
     <t>id</t>
   </si>
@@ -1509,6 +1524,27 @@
   </si>
   <si>
     <t>2015-08-29 - 19-30 Bayern Munich 3 - 0 Bayer Leverkusen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Speaking to fans before the game, they certainly weren't coming into the ground on spy, I don't know whether you felt the same thing, Martin.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大分類</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ダイブンルイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>付加的情報か</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">フカテキ </t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">ジョウホウ </t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1622,6 +1658,10 @@
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="denoised_1_tokenized_224p_annotation" connectionId="3" xr16:uid="{28FAE329-83B7-BB4C-97D0-3BAFBE2A19B7}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="denoised_1_tokenized_224p_annotation" connectionId="4" xr16:uid="{55272BC2-030C-3348-953A-8A68F8120B19}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3727,6 +3767,9 @@
       <c r="E2" s="5" t="s">
         <v>354</v>
       </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="21">
       <c r="A3">
@@ -3744,6 +3787,9 @@
       <c r="E3" s="5" t="s">
         <v>352</v>
       </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="21">
       <c r="A4">
@@ -3761,6 +3807,9 @@
       <c r="E4" s="5" t="s">
         <v>358</v>
       </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="21">
       <c r="A5">
@@ -3778,6 +3827,9 @@
       <c r="E5" s="5" t="s">
         <v>338</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="21">
       <c r="A6">
@@ -3795,6 +3847,9 @@
       <c r="E6" s="5" t="s">
         <v>357</v>
       </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="21">
       <c r="A7">
@@ -3812,6 +3867,9 @@
       <c r="E7" s="5" t="s">
         <v>396</v>
       </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="21">
       <c r="A8">
@@ -3829,6 +3887,9 @@
       <c r="E8" s="5" t="s">
         <v>367</v>
       </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="21">
       <c r="A9">
@@ -3966,7 +4027,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="21">
+    <row r="17" spans="1:7" ht="21">
       <c r="A17">
         <v>707</v>
       </c>
@@ -3983,7 +4044,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="21">
+    <row r="18" spans="1:7" ht="21">
       <c r="A18">
         <v>760</v>
       </c>
@@ -3999,8 +4060,11 @@
       <c r="E18" s="5" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="21">
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21">
       <c r="A19">
         <v>778</v>
       </c>
@@ -4016,8 +4080,14 @@
       <c r="E19" s="5" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="42">
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="42">
       <c r="A20">
         <v>885</v>
       </c>
@@ -4034,7 +4104,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="21">
+    <row r="21" spans="1:7" ht="21">
       <c r="A21">
         <v>890</v>
       </c>
@@ -4051,7 +4121,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="21">
+    <row r="22" spans="1:7" ht="21">
       <c r="A22">
         <v>953</v>
       </c>
@@ -4068,7 +4138,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="21">
+    <row r="23" spans="1:7" ht="21">
       <c r="A23">
         <v>955</v>
       </c>
@@ -4085,7 +4155,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="21">
+    <row r="24" spans="1:7" ht="21">
       <c r="A24">
         <v>960</v>
       </c>
@@ -4102,7 +4172,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="21">
+    <row r="25" spans="1:7" ht="21">
       <c r="A25">
         <v>961</v>
       </c>
@@ -4119,7 +4189,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="21">
+    <row r="26" spans="1:7" ht="21">
       <c r="A26">
         <v>998</v>
       </c>
@@ -4136,7 +4206,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="21">
+    <row r="27" spans="1:7" ht="21">
       <c r="A27">
         <v>1029</v>
       </c>
@@ -4153,7 +4223,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="21">
+    <row r="28" spans="1:7" ht="21">
       <c r="A28">
         <v>1067</v>
       </c>
@@ -4170,7 +4240,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="21">
+    <row r="29" spans="1:7" ht="21">
       <c r="A29">
         <v>1207</v>
       </c>
@@ -4187,7 +4257,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="21">
+    <row r="30" spans="1:7" ht="21">
       <c r="A30">
         <v>1318</v>
       </c>
@@ -4204,7 +4274,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="21">
+    <row r="31" spans="1:7" ht="21">
       <c r="A31">
         <v>1542</v>
       </c>
@@ -4221,7 +4291,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="21">
+    <row r="32" spans="1:7" ht="21">
       <c r="A32">
         <v>1616</v>
       </c>
@@ -5484,7 +5554,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="42">
+    <row r="3" spans="1:8" ht="21">
       <c r="A3">
         <v>132</v>
       </c>
@@ -6697,7 +6767,7 @@
         <v>72</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>73</v>
+        <v>435</v>
       </c>
       <c r="F61" t="s">
         <v>318</v>
@@ -7539,6 +7609,2538 @@
         <v>112</v>
       </c>
       <c r="F101">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19E2283-4772-A846-A5FD-09033F570B60}">
+  <dimension ref="A1:I101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="44.140625" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="21">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="42">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F2" t="b">
+        <f>G2=2</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="21">
+      <c r="A3">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" t="b">
+        <f t="shared" ref="F3:F66" si="0">G3=2</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="21">
+      <c r="A4">
+        <v>230</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="21">
+      <c r="A5">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="F5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="42">
+      <c r="A6">
+        <v>511</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="21">
+      <c r="A7">
+        <v>535</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="63">
+      <c r="A8">
+        <v>576</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" t="b">
+        <f>G8=2</f>
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>1.4</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="21">
+      <c r="A9">
+        <v>833</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="F9" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="21">
+      <c r="A10">
+        <v>970</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="21">
+      <c r="A11">
+        <v>994</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="21">
+      <c r="A12">
+        <v>1079</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="21">
+      <c r="A13">
+        <v>1174</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F13" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="21">
+      <c r="A14">
+        <v>1192</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="21">
+      <c r="A15">
+        <v>1425</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="21">
+      <c r="A16">
+        <v>1543</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="21">
+      <c r="A17">
+        <v>1554</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F17" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="21">
+      <c r="A18">
+        <v>1569</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="21">
+      <c r="A19">
+        <v>1615</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F19" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="21">
+      <c r="A20">
+        <v>1694</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="21">
+      <c r="A21">
+        <v>1703</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="21">
+      <c r="A22">
+        <v>1730</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F22" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="21">
+      <c r="A23">
+        <v>1864</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="21">
+      <c r="A24">
+        <v>1922</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F24" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="21">
+      <c r="A25">
+        <v>1934</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F25" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="21">
+      <c r="A26">
+        <v>2034</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="21">
+      <c r="A27">
+        <v>2080</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="F27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="21">
+      <c r="A28">
+        <v>2098</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F28" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="21">
+      <c r="A29">
+        <v>2107</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="21">
+      <c r="A30">
+        <v>2132</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F30" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="21">
+      <c r="A31">
+        <v>2155</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F31" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="21">
+      <c r="A32">
+        <v>2323</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F32" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="42">
+      <c r="A33">
+        <v>2576</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="F33" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="42">
+      <c r="A34">
+        <v>2585</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="21">
+      <c r="A35">
+        <v>2650</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F35" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="21">
+      <c r="A36">
+        <v>2678</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F36" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="21">
+      <c r="A37">
+        <v>2764</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="21">
+      <c r="A38">
+        <v>2771</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="42">
+      <c r="A39">
+        <v>2789</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="21">
+      <c r="A40">
+        <v>2865</v>
+      </c>
+      <c r="B40" t="s">
+        <v>434</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F40" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="42">
+      <c r="A41">
+        <v>2957</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="21">
+      <c r="A42">
+        <v>3114</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F42" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="21">
+      <c r="A43">
+        <v>3121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F43" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="21">
+      <c r="A44">
+        <v>3231</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F44" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="21">
+      <c r="A45">
+        <v>3257</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F45" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="21">
+      <c r="A46">
+        <v>3290</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="F46" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="21">
+      <c r="A47">
+        <v>3312</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F47" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="21">
+      <c r="A48">
+        <v>3381</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F48" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="21">
+      <c r="A49">
+        <v>3492</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F49" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="21">
+      <c r="A50">
+        <v>3509</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="21">
+      <c r="A51">
+        <v>3612</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F51" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="21">
+      <c r="A52">
+        <v>3662</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F52" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="21">
+      <c r="A53">
+        <v>3787</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F53" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+      <c r="H53">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="21">
+      <c r="A54">
+        <v>3837</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="21">
+      <c r="A55">
+        <v>3901</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F55" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="21">
+      <c r="A56">
+        <v>4094</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F56" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="84">
+      <c r="A57">
+        <v>4119</v>
+      </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F57" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="21">
+      <c r="A58">
+        <v>4204</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F58" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="21">
+      <c r="A59">
+        <v>4333</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F59" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="21">
+      <c r="A60">
+        <v>4498</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F60" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="42">
+      <c r="A61">
+        <v>4541</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F61" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61">
+        <v>3.3</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="21">
+      <c r="A62">
+        <v>4556</v>
+      </c>
+      <c r="B62" t="s">
+        <v>432</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F62" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
+      </c>
+      <c r="H62">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="21">
+      <c r="A63">
+        <v>4608</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F63" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>2</v>
+      </c>
+      <c r="H63">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="42">
+      <c r="A64">
+        <v>4649</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F64" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="21">
+      <c r="A65">
+        <v>4667</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F65" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="21">
+      <c r="A66">
+        <v>4705</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="21">
+      <c r="A67">
+        <v>4866</v>
+      </c>
+      <c r="B67" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F67" t="b">
+        <f t="shared" ref="F67:F101" si="1">G67=2</f>
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="21">
+      <c r="A68">
+        <v>4898</v>
+      </c>
+      <c r="B68" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F68" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="21">
+      <c r="A69">
+        <v>5025</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F69" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="21">
+      <c r="A70">
+        <v>5033</v>
+      </c>
+      <c r="B70" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F70" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>2</v>
+      </c>
+      <c r="H70">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="21">
+      <c r="A71">
+        <v>5058</v>
+      </c>
+      <c r="B71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F71" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="21">
+      <c r="A72">
+        <v>5160</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F72" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="21">
+      <c r="A73">
+        <v>5170</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F73" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="21">
+      <c r="A74">
+        <v>5204</v>
+      </c>
+      <c r="B74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="F74" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="21">
+      <c r="A75">
+        <v>5275</v>
+      </c>
+      <c r="B75" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F75" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>3</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="21">
+      <c r="A76">
+        <v>5347</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F76" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="21">
+      <c r="A77">
+        <v>5371</v>
+      </c>
+      <c r="B77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F77" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="21">
+      <c r="A78">
+        <v>5538</v>
+      </c>
+      <c r="B78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F78" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="21">
+      <c r="A79">
+        <v>5640</v>
+      </c>
+      <c r="B79" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F79" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="42">
+      <c r="A80">
+        <v>5663</v>
+      </c>
+      <c r="B80" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F80" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="21">
+      <c r="A81">
+        <v>5666</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F81" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="21">
+      <c r="A82">
+        <v>5712</v>
+      </c>
+      <c r="B82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F82" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="21">
+      <c r="A83">
+        <v>5770</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F83" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="21">
+      <c r="A84">
+        <v>5924</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F84" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>3</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="21">
+      <c r="A85">
+        <v>5954</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F85" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="21">
+      <c r="A86">
+        <v>5995</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F86" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="21">
+      <c r="A87">
+        <v>6040</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F87" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>3</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="21">
+      <c r="A88">
+        <v>6062</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F88" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="21">
+      <c r="A89">
+        <v>6068</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F89" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="21">
+      <c r="A90">
+        <v>6119</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F90" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>2</v>
+      </c>
+      <c r="H90">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="21">
+      <c r="A91">
+        <v>6139</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F91" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="21">
+      <c r="A92">
+        <v>6151</v>
+      </c>
+      <c r="B92" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F92" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="21">
+      <c r="A93">
+        <v>6158</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F93" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="21">
+      <c r="A94">
+        <v>6288</v>
+      </c>
+      <c r="B94" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="F94" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="21">
+      <c r="A95">
+        <v>6377</v>
+      </c>
+      <c r="B95" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F95" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="21">
+      <c r="A96">
+        <v>6404</v>
+      </c>
+      <c r="B96" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F96" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="21">
+      <c r="A97">
+        <v>6446</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F97" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="21">
+      <c r="A98">
+        <v>6559</v>
+      </c>
+      <c r="B98" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F98" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="21">
+      <c r="A99">
+        <v>6721</v>
+      </c>
+      <c r="B99" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F99" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="21">
+      <c r="A100">
+        <v>6810</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F100" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="21">
+      <c r="A101">
+        <v>6881</v>
+      </c>
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F101" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G101">
         <v>1</v>
       </c>
     </row>

--- a/annotation_tool/annotation_template.xlsx
+++ b/annotation_tool/annotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/heste/workspace/sn-caption/annotation_tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC213EB-103A-F94C-9B0A-F02FED668E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D947A248-97CB-344A-80B5-91247A2CD87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31180" yWindow="4740" windowWidth="25600" windowHeight="14140" activeTab="3" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
+    <workbookView xWindow="4920" yWindow="-28300" windowWidth="25600" windowHeight="14160" activeTab="3" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート_seed42" sheetId="4" r:id="rId1"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="439">
   <si>
     <t>id</t>
   </si>
@@ -1545,6 +1545,10 @@
     <rPh sb="3" eb="5">
       <t xml:space="preserve">ジョウホウ </t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You can definitely run up to Ludwig, who shows weaknesses more often in the game, the Russian goalkeeper.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7677,7 +7681,7 @@
         <v>222</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>223</v>
+        <v>438</v>
       </c>
       <c r="F2" t="b">
         <f>G2=2</f>
@@ -7714,7 +7718,7 @@
         <v>3</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="21">
@@ -8251,13 +8255,10 @@
       </c>
       <c r="F25" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25">
-        <v>1.1000000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="21">
@@ -9040,10 +9041,13 @@
       </c>
       <c r="F57" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H57">
+        <v>2.2999999999999998</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>427</v>
@@ -9196,13 +9200,10 @@
       </c>
       <c r="F63" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>2</v>
-      </c>
-      <c r="H63">
-        <v>1.1000000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="42">

--- a/annotation_tool/annotation_template.xlsx
+++ b/annotation_tool/annotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/heste/workspace/sn-caption/annotation_tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D947A248-97CB-344A-80B5-91247A2CD87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EE68CA-F914-A04F-B909-C9E43CE926AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="-28300" windowWidth="25600" windowHeight="14160" activeTab="3" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="3" xr2:uid="{89A04599-6038-9D4E-8F37-84B4D23DB047}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート_seed42" sheetId="4" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="denoised_1_tokenized_224p_annotation" localSheetId="0">テンプレート_seed42!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -106,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="440">
   <si>
     <t>id</t>
   </si>
@@ -1549,6 +1550,10 @@
   </si>
   <si>
     <t>You can definitely run up to Ludwig, who shows weaknesses more often in the game, the Russian goalkeeper.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>He's been taken under the wing by Victor Fernandez but he's going to be slightly off the pace whatever and you're going up against arguably the most potent strike force in all of the Liga if not Europe.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7834,7 +7839,7 @@
         <v>234</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>235</v>
+        <v>439</v>
       </c>
       <c r="F8" t="b">
         <f>G8=2</f>
